--- a/ig/test-tabs-svs/ValueSet-jdv-j376-public-activite-smsse-regulee-rass.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j376-public-activite-smsse-regulee-rass.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="217">
   <si>
     <t>Property</t>
   </si>
@@ -131,7 +131,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r403-public-activite-smsse-regulee|20260223120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r403-public-activite-smsse-regulee|20260629120000</t>
   </si>
   <si>
     <t>version</t>
@@ -170,6 +170,12 @@
     <t>Adolescents ASE (7-17 ans)</t>
   </si>
   <si>
+    <t>842</t>
+  </si>
+  <si>
+    <t>Adultes (sans autre indication)</t>
+  </si>
+  <si>
     <t>441</t>
   </si>
   <si>
@@ -296,6 +302,12 @@
     <t>Enfants d'Age Préscolaire</t>
   </si>
   <si>
+    <t>843</t>
+  </si>
+  <si>
+    <t>Enfants et adolescents (sans autre indication)</t>
+  </si>
+  <si>
     <t>807</t>
   </si>
   <si>
@@ -434,6 +446,12 @@
     <t>Parents en difficulté avec enfant</t>
   </si>
   <si>
+    <t>844</t>
+  </si>
+  <si>
+    <t>Patients de soins sans consentement</t>
+  </si>
+  <si>
     <t>834</t>
   </si>
   <si>
@@ -576,6 +594,12 @@
   </si>
   <si>
     <t>Prostituées avec ou sans Enfant</t>
+  </si>
+  <si>
+    <t>841</t>
+  </si>
+  <si>
+    <t>Périnatalité</t>
   </si>
   <si>
     <t>815</t>
@@ -1002,7 +1026,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -2729,6 +2753,90 @@
         <v>15</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="E83" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="F83" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="E84" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="F84" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="E85" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="F85" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="E86" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
